--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:08</t>
+    <t xml:space="preserve">2026-09-24 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -570,19 +570,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.65</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.41</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="3">
@@ -593,19 +593,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.09</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="4">
@@ -616,19 +616,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.64</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.35</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="5">
@@ -639,19 +639,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.28</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="6">
@@ -662,19 +662,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.78</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="7">
@@ -894,19 +894,19 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="19">
@@ -917,19 +917,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.48</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.56</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="20">
@@ -940,19 +940,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.43</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="21">
@@ -963,19 +963,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.62</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.16</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="22">
@@ -986,19 +986,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.57</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.31</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="23">
@@ -1009,19 +1009,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.47</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.13</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="24">
@@ -1055,19 +1055,19 @@
         <v>31</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.16</v>
+        <v>0.79</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26">
@@ -1078,19 +1078,19 @@
         <v>31</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.73</v>
+        <v>-0.47</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>-0.13</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:57</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">plot_regional_correl_matriz_m_movinterna_a_2024_magallanes.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 20:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
